--- a/src/pandorafits/formats/visda/level2-headers.xlsx
+++ b/src/pandorafits/formats/visda/level2-headers.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chedges/Pandora/repos/pandora-fits/src/pandorafits/fileformats/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chedges/Pandora/repos/pandora-fits/src/pandorafits/formats/visda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE50B32E-EF12-9443-AC72-D87E79795F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{130660FF-6988-E64E-B0BC-13231198914A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2200" yWindow="760" windowWidth="28040" windowHeight="17060" activeTab="4" xr2:uid="{B6A127EC-86E5-1348-8EA3-CDC4E3346098}"/>
+    <workbookView xWindow="2200" yWindow="760" windowWidth="28040" windowHeight="17060" activeTab="1" xr2:uid="{B6A127EC-86E5-1348-8EA3-CDC4E3346098}"/>
   </bookViews>
   <sheets>
     <sheet name="Primary" sheetId="4" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="184">
   <si>
     <t>SIMPLE</t>
   </si>
@@ -93,9 +93,6 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Value</t>
-  </si>
-  <si>
     <t>Comment</t>
   </si>
   <si>
@@ -547,13 +544,61 @@
   </si>
   <si>
     <t>APERTURE</t>
+  </si>
+  <si>
+    <t>Fixed Value</t>
+  </si>
+  <si>
+    <t>Example Value</t>
+  </si>
+  <si>
+    <t>Pandora DPC</t>
+  </si>
+  <si>
+    <t>v0.1.0</t>
+  </si>
+  <si>
+    <t>TUNIT2</t>
+  </si>
+  <si>
+    <t>TUNIT3</t>
+  </si>
+  <si>
+    <t>TUNIT4</t>
+  </si>
+  <si>
+    <t>TUNIT5</t>
+  </si>
+  <si>
+    <t>TUNIT6</t>
+  </si>
+  <si>
+    <t>TUNIT7</t>
+  </si>
+  <si>
+    <t>ppm</t>
+  </si>
+  <si>
+    <t>volt</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>arcsecond</t>
+  </si>
+  <si>
+    <t>PCOUNT</t>
+  </si>
+  <si>
+    <t>GCOUNT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -581,6 +626,12 @@
       <name val="Helvetica"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -602,12 +653,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -942,203 +994,261 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D1C3A0A-8A3B-0648-AAEB-8D3739DF90A8}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="41.5" customWidth="1"/>
-    <col min="3" max="3" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="b">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
       <c r="B7">
         <v>3</v>
       </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="C8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="C9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+      <c r="D10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+      <c r="D11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+      <c r="D12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+        <v>171</v>
+      </c>
+      <c r="D13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="C14" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C14">
+        <v>153.71574452308701</v>
+      </c>
+      <c r="D14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>15</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15">
+        <v>-47.156720216140499</v>
+      </c>
+      <c r="D15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16">
         <v>40</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+      <c r="D16" t="s">
         <v>42</v>
       </c>
-      <c r="C16" t="s">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+      <c r="C17">
+        <v>40</v>
+      </c>
+      <c r="D17" t="s">
         <v>44</v>
       </c>
-      <c r="C17" t="s">
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
         <v>46</v>
       </c>
-      <c r="C18" t="s">
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
+      <c r="C19">
+        <v>0.2</v>
+      </c>
+      <c r="D19" t="s">
         <v>48</v>
       </c>
-      <c r="C19" t="s">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+      <c r="C20">
+        <v>32</v>
+      </c>
+      <c r="D20" t="s">
         <v>50</v>
       </c>
-      <c r="C20" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21">
+        <v>1000</v>
+      </c>
+      <c r="D21" t="s">
         <v>63</v>
-      </c>
-      <c r="C21" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1148,411 +1258,485 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A83271CB-FC54-E142-86E3-37282DC63805}">
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
         <v>20</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>183</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>32</v>
+      </c>
+      <c r="C6">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" t="s">
+        <v>156</v>
+      </c>
+      <c r="C11" t="s">
+        <v>156</v>
+      </c>
+      <c r="D11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" t="b">
+        <v>1</v>
+      </c>
+      <c r="C12" t="b">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
         <v>29</v>
       </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>32</v>
-      </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>74</v>
+      </c>
+      <c r="D20" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>77</v>
+      </c>
+      <c r="B22" t="s">
         <v>157</v>
       </c>
-      <c r="C8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" t="b">
-        <v>1</v>
-      </c>
-      <c r="C9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B10">
-        <v>2</v>
-      </c>
-      <c r="C10" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
+      <c r="C22" t="s">
+        <v>157</v>
+      </c>
+      <c r="D22" t="s">
         <v>78</v>
       </c>
-      <c r="B19" t="s">
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>79</v>
+      </c>
+      <c r="B23" t="s">
+        <v>157</v>
+      </c>
+      <c r="C23" t="s">
+        <v>157</v>
+      </c>
+      <c r="D23" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" t="s">
         <v>158</v>
       </c>
-      <c r="C19" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>80</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="C24" t="s">
         <v>158</v>
       </c>
-      <c r="C20" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
+      <c r="D24" t="s">
         <v>81</v>
       </c>
-      <c r="B21" t="s">
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" t="s">
         <v>159</v>
       </c>
-      <c r="C21" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+      <c r="C25" t="s">
+        <v>159</v>
+      </c>
+      <c r="D25" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
         <v>83</v>
       </c>
-      <c r="B22" t="s">
+      <c r="D26" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>85</v>
+      </c>
+      <c r="D27" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>86</v>
+      </c>
+      <c r="D28" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>88</v>
+      </c>
+      <c r="D29" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>90</v>
+      </c>
+      <c r="D30" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>92</v>
+      </c>
+      <c r="B31" t="s">
         <v>160</v>
       </c>
-      <c r="C22" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>84</v>
-      </c>
-      <c r="C23" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>86</v>
-      </c>
-      <c r="C24" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>87</v>
-      </c>
-      <c r="C25" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C26" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>91</v>
-      </c>
-      <c r="C27" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
+      <c r="C31" t="s">
+        <v>160</v>
+      </c>
+      <c r="D31" t="s">
         <v>93</v>
       </c>
-      <c r="B28" t="s">
-        <v>161</v>
-      </c>
-      <c r="C28" t="s">
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+      <c r="B32">
+        <v>2000</v>
+      </c>
+      <c r="C32">
+        <v>2000</v>
+      </c>
+      <c r="D32" t="s">
         <v>95</v>
       </c>
-      <c r="B29">
-        <v>2000</v>
-      </c>
-      <c r="C29" t="s">
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
+      <c r="D33" t="s">
         <v>97</v>
       </c>
-      <c r="C30" t="s">
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
+      <c r="D34" t="s">
         <v>99</v>
       </c>
-      <c r="C31" t="s">
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
+      <c r="D35" t="s">
         <v>101</v>
       </c>
-      <c r="C32" t="s">
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
+      <c r="D36" t="s">
         <v>103</v>
       </c>
-      <c r="C33" t="s">
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
+      <c r="D37" t="s">
         <v>105</v>
       </c>
-      <c r="C34" t="s">
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
+      <c r="D38" t="s">
         <v>107</v>
       </c>
-      <c r="C35" t="s">
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
+      <c r="D39" t="s">
         <v>109</v>
       </c>
-      <c r="C36" t="s">
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
+      <c r="D40" t="s">
         <v>111</v>
       </c>
-      <c r="C37" t="s">
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
+      <c r="D41" t="s">
         <v>113</v>
       </c>
-      <c r="C38" t="s">
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
+      <c r="D42" t="s">
         <v>115</v>
       </c>
-      <c r="C39" t="s">
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
+      <c r="D43" t="s">
         <v>117</v>
       </c>
-      <c r="C40" t="s">
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
+      <c r="D44" t="s">
         <v>119</v>
       </c>
-      <c r="C41" t="s">
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
+      <c r="D45" t="s">
         <v>121</v>
       </c>
-      <c r="C42" t="s">
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
+      <c r="D46" t="s">
         <v>123</v>
       </c>
-      <c r="C43" t="s">
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
+      <c r="D47" t="s">
         <v>125</v>
       </c>
-      <c r="C44" t="s">
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
+      <c r="D48" t="s">
         <v>127</v>
-      </c>
-      <c r="C45" t="s">
-        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -1562,99 +1746,137 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA5C7CA0-9B51-E440-9CB8-62CC3EA7964F}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" customWidth="1"/>
+    <col min="4" max="4" width="23.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" t="s">
         <v>20</v>
       </c>
-      <c r="B2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="C7">
+        <v>50</v>
+      </c>
+      <c r="D7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>22</v>
       </c>
-      <c r="B5">
+      <c r="C8">
         <v>50</v>
       </c>
-      <c r="C5">
+      <c r="D8">
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>23</v>
       </c>
-      <c r="B6">
-        <v>50</v>
-      </c>
-      <c r="C6">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="C9">
+        <v>9</v>
+      </c>
+      <c r="D9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" t="s">
+        <v>167</v>
+      </c>
+      <c r="C10" t="s">
+        <v>167</v>
+      </c>
+      <c r="D10" t="s">
         <v>24</v>
-      </c>
-      <c r="B7">
-        <v>9</v>
-      </c>
-      <c r="C7">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>168</v>
-      </c>
-      <c r="C8" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1664,102 +1886,140 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFF9BC8E-79D6-3D4F-A83E-F2C79C6EF671}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" t="s">
         <v>20</v>
       </c>
-      <c r="B2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
+      <c r="C7">
+        <v>50</v>
+      </c>
+      <c r="D7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B5">
+      <c r="C8">
         <v>50</v>
       </c>
-      <c r="C5">
+      <c r="D8">
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B6">
-        <v>50</v>
-      </c>
-      <c r="C6">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+      <c r="C9">
+        <v>9</v>
+      </c>
+      <c r="D9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" t="s">
+        <v>128</v>
+      </c>
+      <c r="C10" t="s">
+        <v>128</v>
+      </c>
+      <c r="D10" t="s">
         <v>24</v>
       </c>
-      <c r="B7">
-        <v>9</v>
-      </c>
-      <c r="C7">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>129</v>
-      </c>
-      <c r="C8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="2"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1768,318 +2028,455 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8EBF481-E44A-834F-A33B-E0886CC2A2D3}">
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5" customWidth="1"/>
+    <col min="4" max="4" width="25.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7">
+        <v>175</v>
+      </c>
+      <c r="C7">
+        <v>175</v>
+      </c>
+      <c r="D7" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>-64</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>22</v>
       </c>
-      <c r="B5">
+      <c r="C8">
+        <v>100</v>
+      </c>
+      <c r="D8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C10" t="s">
+        <v>152</v>
+      </c>
+      <c r="D10" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" t="s">
+        <v>154</v>
+      </c>
+      <c r="C12" t="s">
+        <v>154</v>
+      </c>
+      <c r="D12" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" t="s">
+        <v>155</v>
+      </c>
+      <c r="C14" t="s">
+        <v>155</v>
+      </c>
+      <c r="D14" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>172</v>
+      </c>
+      <c r="B17" t="s">
+        <v>178</v>
+      </c>
+      <c r="C17" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>132</v>
+      </c>
+      <c r="B18" t="s">
+        <v>161</v>
+      </c>
+      <c r="C18" t="s">
+        <v>161</v>
+      </c>
+      <c r="D18" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D19" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>173</v>
+      </c>
+      <c r="B21" t="s">
+        <v>179</v>
+      </c>
+      <c r="C21" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>136</v>
+      </c>
+      <c r="B22" t="s">
+        <v>162</v>
+      </c>
+      <c r="C22" t="s">
+        <v>162</v>
+      </c>
+      <c r="D22" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>138</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D23" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>174</v>
+      </c>
+      <c r="B25" t="s">
+        <v>180</v>
+      </c>
+      <c r="C25" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>140</v>
+      </c>
+      <c r="B26" t="s">
+        <v>163</v>
+      </c>
+      <c r="C26" t="s">
+        <v>163</v>
+      </c>
+      <c r="D26" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>142</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
         <v>175</v>
       </c>
-      <c r="C5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B7">
-        <v>7</v>
-      </c>
-      <c r="C7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="B29" t="s">
+        <v>181</v>
+      </c>
+      <c r="C29" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>144</v>
+      </c>
+      <c r="B30" t="s">
+        <v>164</v>
+      </c>
+      <c r="C30" t="s">
+        <v>164</v>
+      </c>
+      <c r="D30" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>146</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C8" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" t="s">
-        <v>155</v>
-      </c>
-      <c r="C10" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>59</v>
-      </c>
-      <c r="B12" t="s">
-        <v>156</v>
-      </c>
-      <c r="C12" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>60</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>61</v>
-      </c>
-      <c r="C14">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>133</v>
-      </c>
-      <c r="B15" t="s">
-        <v>162</v>
-      </c>
-      <c r="C15" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>135</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C16" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>136</v>
-      </c>
-      <c r="C17">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>137</v>
-      </c>
-      <c r="B18" t="s">
-        <v>163</v>
-      </c>
-      <c r="C18" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>139</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C19" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>140</v>
-      </c>
-      <c r="C20">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>141</v>
-      </c>
-      <c r="B21" t="s">
-        <v>164</v>
-      </c>
-      <c r="C21" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>143</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>144</v>
-      </c>
-      <c r="C23">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>145</v>
-      </c>
-      <c r="B24" t="s">
+      <c r="C31" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>176</v>
+      </c>
+      <c r="B33" t="s">
+        <v>181</v>
+      </c>
+      <c r="C33" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>148</v>
+      </c>
+      <c r="B34" t="s">
         <v>165</v>
       </c>
-      <c r="C24" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>147</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>148</v>
-      </c>
-      <c r="C26">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+      <c r="C34" t="s">
+        <v>165</v>
+      </c>
+      <c r="D34" t="s">
         <v>149</v>
       </c>
-      <c r="B27" t="s">
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>150</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>177</v>
+      </c>
+      <c r="B37" t="s">
+        <v>181</v>
+      </c>
+      <c r="C37" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" t="s">
         <v>166</v>
       </c>
-      <c r="C27" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>151</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>152</v>
-      </c>
-      <c r="C29">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>6</v>
-      </c>
-      <c r="B30" t="s">
-        <v>167</v>
-      </c>
-      <c r="C30" t="s">
-        <v>167</v>
+      <c r="C38" t="s">
+        <v>166</v>
+      </c>
+      <c r="D38" t="s">
+        <v>166</v>
       </c>
     </row>
   </sheetData>
